--- a/merged_b3_full_cypress_coverage.xlsx
+++ b/merged_b3_full_cypress_coverage.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -759,7 +759,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -2899,7 +2899,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
@@ -4075,7 +4075,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
